--- a/artfynd/A 3809-2024 artfynd.xlsx
+++ b/artfynd/A 3809-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120323080</v>
+        <v>120323081</v>
       </c>
       <c r="B2" t="n">
         <v>97847</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494764</v>
+        <v>494762</v>
       </c>
       <c r="R2" t="n">
-        <v>6671506</v>
+        <v>6671517</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120323081</v>
+        <v>120323080</v>
       </c>
       <c r="B4" t="n">
         <v>97847</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494762</v>
+        <v>494764</v>
       </c>
       <c r="R4" t="n">
-        <v>6671517</v>
+        <v>6671506</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 3809-2024 artfynd.xlsx
+++ b/artfynd/A 3809-2024 artfynd.xlsx
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120323083</v>
+        <v>120323080</v>
       </c>
       <c r="B3" t="n">
         <v>97847</v>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494755</v>
+        <v>494764</v>
       </c>
       <c r="R3" t="n">
-        <v>6671527</v>
+        <v>6671506</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120323080</v>
+        <v>120323083</v>
       </c>
       <c r="B4" t="n">
         <v>97847</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494764</v>
+        <v>494755</v>
       </c>
       <c r="R4" t="n">
-        <v>6671506</v>
+        <v>6671527</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 3809-2024 artfynd.xlsx
+++ b/artfynd/A 3809-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120323081</v>
+        <v>120323080</v>
       </c>
       <c r="B2" t="n">
         <v>97847</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494762</v>
+        <v>494764</v>
       </c>
       <c r="R2" t="n">
-        <v>6671517</v>
+        <v>6671506</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120323080</v>
+        <v>120323083</v>
       </c>
       <c r="B3" t="n">
         <v>97847</v>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494764</v>
+        <v>494755</v>
       </c>
       <c r="R3" t="n">
-        <v>6671506</v>
+        <v>6671527</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120323083</v>
+        <v>120323081</v>
       </c>
       <c r="B4" t="n">
         <v>97847</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494755</v>
+        <v>494762</v>
       </c>
       <c r="R4" t="n">
-        <v>6671527</v>
+        <v>6671517</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 3809-2024 artfynd.xlsx
+++ b/artfynd/A 3809-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120323080</v>
+        <v>120323083</v>
       </c>
       <c r="B2" t="n">
         <v>97847</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494764</v>
+        <v>494755</v>
       </c>
       <c r="R2" t="n">
-        <v>6671506</v>
+        <v>6671527</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -781,7 +781,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120323083</v>
+        <v>120323081</v>
       </c>
       <c r="B3" t="n">
         <v>97847</v>
@@ -825,10 +825,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494755</v>
+        <v>494762</v>
       </c>
       <c r="R3" t="n">
-        <v>6671527</v>
+        <v>6671517</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120323081</v>
+        <v>120323080</v>
       </c>
       <c r="B4" t="n">
         <v>97847</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494762</v>
+        <v>494764</v>
       </c>
       <c r="R4" t="n">
-        <v>6671517</v>
+        <v>6671506</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 3809-2024 artfynd.xlsx
+++ b/artfynd/A 3809-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120323083</v>
+        <v>120323080</v>
       </c>
       <c r="B2" t="n">
         <v>97847</v>
@@ -719,10 +719,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494755</v>
+        <v>494764</v>
       </c>
       <c r="R2" t="n">
-        <v>6671527</v>
+        <v>6671506</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -887,7 +887,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120323080</v>
+        <v>120323083</v>
       </c>
       <c r="B4" t="n">
         <v>97847</v>
@@ -931,10 +931,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494764</v>
+        <v>494755</v>
       </c>
       <c r="R4" t="n">
-        <v>6671506</v>
+        <v>6671527</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>

--- a/artfynd/A 3809-2024 artfynd.xlsx
+++ b/artfynd/A 3809-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,42 +675,52 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>120323081</v>
+        <v>121428133</v>
       </c>
       <c r="B2" t="n">
-        <v>97931</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>219790</v>
+        <v>205998</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>detektor med heterodyn</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -719,13 +729,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>494762</v>
+        <v>494777</v>
       </c>
       <c r="R2" t="n">
-        <v>6671517</v>
+        <v>6671526</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +759,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-06-19</t>
+          <t>2024-07-11</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,27 +779,26 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Oskar Persson</t>
+          <t>Adina Sennblad (AFRY)</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Oskar Persson, Elliot Örjes, Frida Sjöborg, Eduardo Ottimofiore</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+          <t>Adina Sennblad (AFRY), Lars Bohlin</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>Artkartering Fladdermöss Låsberget</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>120323083</v>
+        <v>120323075</v>
       </c>
       <c r="B3" t="n">
-        <v>97931</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -825,10 +834,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>494755</v>
+        <v>494777</v>
       </c>
       <c r="R3" t="n">
-        <v>6671527</v>
+        <v>6671407</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -880,22 +889,17 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Oskar Persson, Elliot Örjes, Frida Sjöborg, Eduardo Ottimofiore</t>
+          <t>Oskar Persson, Eduardo Ottimofiore, Frida Sjöborg, Elliot Örjes</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>120323080</v>
+        <v>120323077</v>
       </c>
       <c r="B4" t="n">
-        <v>97931</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -931,10 +935,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>494764</v>
+        <v>494783</v>
       </c>
       <c r="R4" t="n">
-        <v>6671506</v>
+        <v>6671443</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -986,10 +990,515 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Oskar Persson, Elliot Örjes, Frida Sjöborg, Eduardo Ottimofiore</t>
+          <t>Oskar Persson, Eduardo Ottimofiore, Frida Sjöborg, Elliot Örjes</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120323078</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Låsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>494773</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6671463</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Oskar Persson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Oskar Persson, Eduardo Ottimofiore, Frida Sjöborg, Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120323079</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Låsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>494769</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6671490</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Oskar Persson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Oskar Persson, Eduardo Ottimofiore, Frida Sjöborg, Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120323080</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Låsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>494764</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6671506</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Oskar Persson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Oskar Persson, Eduardo Ottimofiore, Frida Sjöborg, Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120323081</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Låsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>494762</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6671517</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Oskar Persson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Oskar Persson, Eduardo Ottimofiore, Frida Sjöborg, Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120323083</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Låsberget, Dlr</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>494755</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6671527</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-06-19</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Oskar Persson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Oskar Persson, Eduardo Ottimofiore, Frida Sjöborg, Elliot Örjes</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
